--- a/www/download/COUNTRY.CAN.rpA2.xlsx
+++ b/www/download/COUNTRY.CAN.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Canadá</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>1.3720432596379</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>1.36338223708724</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>1.38427460943857</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1.48183278744543</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>1.48566336709342</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>1.48453859679937</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>1.5482992862423</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>1.56897207355012</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.39701876991229</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>1.29873500614905</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>1.21096172036363</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>1.13405687946817</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>1.06932430176669</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>1.06056911664981</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>1.13781952754438</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13.593</t>
+          <t>3.32524827856153</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13.739</t>
+          <t>3.24158999564283</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14.028</t>
+          <t>3.35378437118849</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14.345</t>
+          <t>3.12262593151385</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>2.90886188840833</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>15.048</t>
+          <t>2.61907599303805</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15.199</t>
+          <t>2.38922762804552</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15.568</t>
+          <t>2.34398406722136</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>15.902</t>
+          <t>2.18466879193273</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>16.166</t>
+          <t>2.06659510348326</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>16.405</t>
+          <t>1.912390933761</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>16.677</t>
+          <t>1.8118245150071</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>17.047</t>
+          <t>1.93053074029023</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>17.486</t>
+          <t>1.95359127274544</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>16.875</t>
+          <t>2.2065734193723</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12.163</t>
+          <t>1.3339010931221</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12.209</t>
+          <t>1.41843148716089</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12.429</t>
+          <t>1.57129325279384</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>1.43792335825647</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>13.076</t>
+          <t>1.34538438922849</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13.48</t>
+          <t>1.15403735581899</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13.708</t>
+          <t>1.03782446626119</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.048</t>
+          <t>1.04779997326747</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14.355</t>
+          <t>0.922291490934717</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>14.633</t>
+          <t>0.847857280559042</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>14.847</t>
+          <t>0.726169892756439</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>15.135</t>
+          <t>0.677045964087077</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>15.444</t>
+          <t>0.729986146785261</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>15.745</t>
+          <t>0.720377552719349</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>15.433</t>
+          <t>0.826405195997246</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24163.261</t>
+          <t>0.186792799366903</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24606.801</t>
+          <t>0.237566238709078</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24972.061</t>
+          <t>0.280800342046428</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>25524.081</t>
+          <t>0.22688834024631</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>26167.659</t>
+          <t>0.193219149581352</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>26709.975</t>
+          <t>0.10970849798421</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>26868.102</t>
+          <t>0.0476027020162406</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27201.949</t>
+          <t>0.0690111495819508</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>27611.262</t>
+          <t>0.0228259312858827</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>28349.86</t>
+          <t>-0.0113456308598275</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>28533.803</t>
+          <t>-0.070083894350059</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>28986.532</t>
+          <t>-0.10061059411134</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>29625.12</t>
+          <t>-0.0705134391697892</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>30221.823</t>
+          <t>-0.0628510337984414</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>28824.294</t>
+          <t>-0.0165780092000315</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21474.27</t>
+          <t>69489325900.7502</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>21728.47</t>
+          <t>71159300859.4488</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21998.085</t>
+          <t>71431482844.16</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>22407.136</t>
+          <t>72220702549.7846</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>23096.434</t>
+          <t>76046561029.2463</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23762.495</t>
+          <t>83209917185.555</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>24065.074</t>
+          <t>83756389878.6881</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>24452.873</t>
+          <t>81528268637.5876</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>24822.944</t>
+          <t>84631604399.0707</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>25528.033</t>
+          <t>91692925305.6114</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>25761.811</t>
+          <t>94558484683.1147</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>26246.008</t>
+          <t>97653081715.9027</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>26776.738</t>
+          <t>95902740713.3799</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>27188.563</t>
+          <t>97694988723.6861</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>26224.348</t>
+          <t>91963887320.6007</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>24263777152.7062</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>24042335986.5696</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>23160923811.9918</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>24935931988.715</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>26834742951.2363</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>30090509636.3343</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>32387618340.1924</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>32919317976.772</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>35544032340.1917</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>38054234429.9735</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>41101219492.055</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>43299070774.7804</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>42795383140.6557</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>43580868041.7033</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>24.88</t>
+          <t>39495798182.8928</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>77.76</t>
+          <t>2866121.26802803</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>2789061.05050704</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>76.44</t>
+          <t>2708471.68949042</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>76.01</t>
+          <t>2865326.02177288</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>76.56</t>
+          <t>2806829.13329641</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>76.32</t>
+          <t>2717803.24158648</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>2879207.04770186</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>75.35</t>
+          <t>2701673.95913805</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>75.36</t>
+          <t>2430804.06125384</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>74.96</t>
+          <t>2308651.65629386</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>74.58</t>
+          <t>2183468.45055412</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>2021225.82148047</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>73.28</t>
+          <t>1802836.46350754</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>73.81</t>
+          <t>1725136.24219596</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>1814608.86665699</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>145061.916633357</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>147007.638421288</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>147818.699453547</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>147603.432731656</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>154337.180422254</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>159763.153192625</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>152916.830076441</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>156228.408969072</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>169766.493249453</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>189314.280059939</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>204489.406347046</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>217047.671098491</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>248189.949099627</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>272872.953545953</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>247140.038584283</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>303122.816303607</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>309459.573126782</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29.04</t>
+          <t>305522.213036468</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>29.86</t>
+          <t>305090.457102355</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>331448.936096928</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>364739.14175431</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>354158.553183297</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>31.93</t>
+          <t>349168.912235744</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>388070.95843958</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>456021.287855829</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>500212.240726103</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>537652.052021564</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>591924.158727582</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>658702.092015314</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>573123.612707858</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>1.76940602500324</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>69.04</t>
+          <t>1.8382698901191</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>68.74</t>
+          <t>1.99616963676183</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>1.85078422785115</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>1.73610313054803</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>1.53307754112019</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>1.3986750616682</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>66.41</t>
+          <t>1.39960022645412</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>65.98</t>
+          <t>1.27288790472861</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>65.56</t>
+          <t>1.19049819518018</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>64.36</t>
+          <t>1.07144658914383</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>1.01652748443302</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>62.13</t>
+          <t>1.09474858033803</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>62.48</t>
+          <t>1.09810397592225</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>60.95</t>
+          <t>1.26034328500752</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>110870.363944736</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>117244.46371809</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>127007.36102905</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>130067.787332087</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>144686.094520039</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>158998.256033625</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>158423.652491121</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>161117.57311878</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>190360.944477713</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>219271.2613444</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>249238.733171195</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>284574.204390954</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>332123.988034219</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>364655.895246358</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>345954.770618337</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.3720432596379</t>
+          <t>1994.86407951207</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.36338223708724</t>
+          <t>1969.26762983785</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.38427460943857</t>
+          <t>1863.49957972544</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.48183278744543</t>
+          <t>1966.5228066605</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.48566336709342</t>
+          <t>2052.27543608677</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.48453859679937</t>
+          <t>2232.21543731968</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.5482992862423</t>
+          <t>2362.70074896832</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.56897207355012</t>
+          <t>2343.40474715344</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.39701876991229</t>
+          <t>2476.08279536359</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.29873500614905</t>
+          <t>2600.56129194958</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.21096172036363</t>
+          <t>2768.32280616573</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.13405687946817</t>
+          <t>2860.81258585669</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.06932430176669</t>
+          <t>2771.00921224763</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.06056911664981</t>
+          <t>2767.92146098123</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.13781952754438</t>
+          <t>2559.21391930765</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>21987848831.2101</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>23435728111.8745</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>19954724777.7015</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>22053228043.0994</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>28507934340.6474</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>38299448713.9376</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>41012894153.3867</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>38965750295.1913</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>43251213409.1133</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>49251447617.9601</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>53219513245.7925</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>53366567541.1287</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>50864569135.3501</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>50717882626.9599</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>37321355415.4922</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>23846102723.7782</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>24767937763.0642</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>20986082915.651</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>22541798354.8415</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>28479021154.3351</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>38352186980.3997</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>41227856337.606</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>38817902422.6122</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>43652225112.6875</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>49181355051.2858</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>53773698878.2301</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>53865943484.2587</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>51877270902.2838</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>52327144530.2506</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>39384388205.1143</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>-1858253892.56801</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.904</t>
+          <t>-1332209651.18973</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.991</t>
+          <t>-1031358137.94949</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.974</t>
+          <t>-488570311.742164</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.103</t>
+          <t>28913186.3122951</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.248</t>
+          <t>-52738266.4620562</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.293</t>
+          <t>-214962184.219234</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.404</t>
+          <t>147847872.579102</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.882</t>
+          <t>-401011703.574257</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3.334</t>
+          <t>70092566.674225</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>3.792</t>
+          <t>-554185632.437569</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4.335</t>
+          <t>-499375943.129956</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>4.913</t>
+          <t>-1012701766.93366</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>5.281</t>
+          <t>-1609261903.29075</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>-2063032789.62206</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.026</t>
+          <t>5524.58860086325</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>5589.31301935499</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.131</t>
+          <t>5583.3608588918</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.099</t>
+          <t>5606.13220093732</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.188</t>
+          <t>5615.23724542383</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.332</t>
+          <t>5654.37479121627</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.314</t>
+          <t>5667.35136473508</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.336</t>
+          <t>5623.23456194306</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>5627.85863668853</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.798</t>
+          <t>5696.524816471</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2.047</t>
+          <t>5734.43283448108</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2.297</t>
+          <t>5768.90720719192</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.536</t>
+          <t>5804.56761345935</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.698</t>
+          <t>5807.38702232525</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.393</t>
+          <t>5784.70199740483</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>5537.84679217837</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>5601.16910049851</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>5594.08882630442</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>5626.85746909679</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.612</t>
+          <t>5634.30801243138</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.674</t>
+          <t>5677.34508683021</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>5694.60237776595</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>5633.46198480974</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>5640.99340425139</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.925</t>
+          <t>5715.77118631185</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>5736.67181193611</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>5772.65392093577</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.323</t>
+          <t>5809.12905165733</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.407</t>
+          <t>5796.64637339791</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.248</t>
+          <t>5764.70514943313</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>332.52</t>
+          <t>212586.247481861</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>324.16</t>
+          <t>227124.703312745</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>335.38</t>
+          <t>240964.027433186</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>312.26</t>
+          <t>244423.644388295</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>290.89</t>
+          <t>276309.688698034</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>261.91</t>
+          <t>319788.323882874</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>238.92</t>
+          <t>305527.004017058</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>234.4</t>
+          <t>293340.303303088</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>218.47</t>
+          <t>324753.164475383</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>206.66</t>
+          <t>374927.434588916</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>191.24</t>
+          <t>416185.066968156</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>181.18</t>
+          <t>447523.281618681</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>193.05</t>
+          <t>479760.62162081</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>195.36</t>
+          <t>511222.713098214</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>220.66</t>
+          <t>377137.545557467</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>133.39</t>
+          <t>19203707554.5961</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>141.84</t>
+          <t>20184469170.1621</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>157.13</t>
+          <t>20718106926.0723</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>143.79</t>
+          <t>22218797259.0516</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>134.54</t>
+          <t>24075659063.8895</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>115.4</t>
+          <t>26788762025.6747</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>103.78</t>
+          <t>26801920280.4249</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>104.78</t>
+          <t>24671957090.5117</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>92.23</t>
+          <t>24208894403.9241</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>84.79</t>
+          <t>27178870423.4271</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>27270451946.5889</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>67.7</t>
+          <t>27990704945.7665</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>26831442572.8602</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>72.04</t>
+          <t>26774602877.3058</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>82.64</t>
+          <t>20901804431.3706</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>183666.011583961</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>23.76</t>
+          <t>191782.196666642</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>215113.236308681</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>22.69</t>
+          <t>218842.694333262</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19.32</t>
+          <t>238488.834750277</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>263380.937661185</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>251390.990117605</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>248272.018594687</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>277697.277630295</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>315849.234990461</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>355455.46037644</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-10.06</t>
+          <t>394786.217441356</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>429994.463429775</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>465299.236218921</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>381023.52742129</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>75275.99</t>
+          <t>32874749014.8739</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>76955.707</t>
+          <t>33672717980.7292</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>78472.032</t>
+          <t>33905469421.0685</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>80719.606</t>
+          <t>37145071530.6097</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>82935.746</t>
+          <t>41640882240.1985</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>85433.54</t>
+          <t>48412769650.9042</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>86553.144</t>
+          <t>50859890820.9566</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>87702.863</t>
+          <t>49547507825.9882</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>89702.936</t>
+          <t>53527210936.7775</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>92400.986</t>
+          <t>60211764084.9104</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>94112.482</t>
+          <t>64962493804.1123</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>96269.106</t>
+          <t>68965034897.9951</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>99027.352</t>
+          <t>67313949295.3502</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>101358.251</t>
+          <t>68827486391.0518</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>97281.975</t>
+          <t>59040816281.3916</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>67196.251</t>
+          <t>28920.2358979004</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>68238.638</t>
+          <t>35342.5066461028</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>69394.057</t>
+          <t>25850.7911245046</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>71086.962</t>
+          <t>25580.9500550331</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>73422.624</t>
+          <t>37820.8539477569</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>76221.594</t>
+          <t>56407.3862216889</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>77687.372</t>
+          <t>54136.0138994528</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>78993.203</t>
+          <t>45068.2847084017</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>80787.601</t>
+          <t>47055.8868450886</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>83357.732</t>
+          <t>59078.1995984548</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>85138.981</t>
+          <t>60729.6065917159</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>87313.766</t>
+          <t>52737.0641773251</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>89645.568</t>
+          <t>49766.1581910343</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>91437.193</t>
+          <t>45923.4768792928</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>89274.062</t>
+          <t>-3885.98186382232</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>69489.326</t>
+          <t>-13671041460.2778</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>71159.301</t>
+          <t>-13488248810.5671</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>71431.483</t>
+          <t>-13187362494.9962</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>72220.703</t>
+          <t>-14926274271.5581</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>76046.561</t>
+          <t>-17565223176.3091</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>83209.917</t>
+          <t>-21624007625.2295</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>83756.39</t>
+          <t>-24057970540.5317</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>81528.269</t>
+          <t>-24875550735.4765</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>84631.604</t>
+          <t>-29318316532.8534</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>91692.925</t>
+          <t>-33032893661.4833</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>94558.485</t>
+          <t>-37692041857.5235</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>97653.082</t>
+          <t>-40974329952.2286</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>95902.741</t>
+          <t>-40482506722.4901</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>97694.989</t>
+          <t>-42052883513.746</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>91963.887</t>
+          <t>-38139011850.021</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>261876.75135</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>271763.24793</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>277291.81396</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>263817.90514</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>287026.28536</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>324675.87616</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>314180.34</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>314996.00135</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>373546.64455</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>431441.21529</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>497102.37432</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>554050.08225</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>604152.65594</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>642542.9809</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>569907.74515</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>33254.688</t>
+          <t>0.0634860575805272</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>33803.966</t>
+          <t>0.0626198359689101</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>34560.2</t>
+          <t>0.0593078728450991</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>34940.534</t>
+          <t>0.0519870264457783</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>35410.618</t>
+          <t>0.0526148468417143</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>36447.634</t>
+          <t>0.0568109202101358</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>36163.92</t>
+          <t>0.0529643655035631</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>36478.138</t>
+          <t>0.0512149180241871</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>37023.154</t>
+          <t>0.0524905956317425</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>38065.723</t>
+          <t>0.0525857646655903</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>38656.008</t>
+          <t>0.0546633644833151</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>39422.102</t>
+          <t>0.0515202733617078</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>40211.395</t>
+          <t>0.0469386656037578</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>40470.981</t>
+          <t>0.0438077131350801</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>39656.294</t>
+          <t>0.035474469871058</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>305138.4016117</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>314440.841405294</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>327587.594007179</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>321065.947049094</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>338738.67643198</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>367677.601538057</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>368676.021467726</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>378844.950791367</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>445424.810033035</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>506864.549157474</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>575007.827669293</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>655840.40661744</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>729298.239529298</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>780052.462522621</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>691872.689819192</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>24263.777</t>
+          <t>321482.530872517</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>24042.336</t>
+          <t>332555.747059074</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>23160.924</t>
+          <t>344917.178394306</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>24935.932</t>
+          <t>338568.917487131</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>26834.743</t>
+          <t>356999.020180108</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>30090.51</t>
+          <t>386874.946130793</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>32387.618</t>
+          <t>386772.922543959</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>32919.318</t>
+          <t>396942.807451827</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>35544.032</t>
+          <t>466382.371783055</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>38054.234</t>
+          <t>530121.617754663</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>41101.219</t>
+          <t>600740.325966168</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>43299.071</t>
+          <t>683381.60813677</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>42795.383</t>
+          <t>760024.789437084</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>43580.868</t>
+          <t>810776.88984777</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>39495.798</t>
+          <t>719123.923659109</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>176.94</t>
+          <t>1806419.95744152</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>183.83</t>
+          <t>1903619.63119832</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>199.62</t>
+          <t>1991378.04293049</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>185.08</t>
+          <t>1974309.49369325</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>173.61</t>
+          <t>2102640.56365441</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>153.31</t>
+          <t>2247626.8056084</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>139.87</t>
+          <t>2293100.26203844</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>139.96</t>
+          <t>2404134.85737192</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>127.29</t>
+          <t>2881662.72184117</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>119.05</t>
+          <t>3334460.74685826</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>107.14</t>
+          <t>3792269.76059826</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>101.65</t>
+          <t>4335280.5429461</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>109.47</t>
+          <t>4912526.2304056</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>109.81</t>
+          <t>5281158.21733246</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>126.03</t>
+          <t>5149659.56775567</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2.866</t>
+          <t>321482.530872517</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.789</t>
+          <t>325947.319473765</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.708</t>
+          <t>337774.685696424</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.865</t>
+          <t>354495.063303018</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.807</t>
+          <t>370432.395051855</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.718</t>
+          <t>389518.440916313</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.879</t>
+          <t>399415.982245792</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.702</t>
+          <t>407788.363459725</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.431</t>
+          <t>416467.695270609</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.309</t>
+          <t>429290.936956204</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.183</t>
+          <t>443943.509142482</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.021</t>
+          <t>459601.081846804</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.803</t>
+          <t>475828.49606592</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.725</t>
+          <t>488962.806655198</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>499029.311942886</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>305138.4016117</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>308275.056795181</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>321007.019242775</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>336496.742908036</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>351598.89165083</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>370233.953189679</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>381068.09338081</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>389693.276346741</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>398201.367691238</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>410914.101583178</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>425256.813912926</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>441754.755068389</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>457487.151721281</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>471507.090284196</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>481214.226599935</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>225552.845377483</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>236448.812770926</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>245111.756785694</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>232706.267192869</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>255316.205739892</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>286688.003149207</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>279876.252906041</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>284245.142758173</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>341621.137156945</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>394616.429465337</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>456536.957313832</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>507929.04306323</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>562711.414032916</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>596011.35945223</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>528636.213800891</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>67196250636.0404</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>68238638318.8073</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>69394056684.8441</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>71086961620.1977</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>73422624196.3294</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>76221594160.6591</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>77687372419.4473</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>78993202871.7772</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>80787601191.3044</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>83357731837.8204</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>85138980926.4693</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>87313766267.7553</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>89645568078.9108</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>91437192512.4405</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>89274062208.7139</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>75275989507.9021</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>76955706645.5813</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>78472031995.5129</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>80719605529.9711</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>82935746212.5312</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>85433540457.0861</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>86553144191.8719</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>87702862860.8171</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>89702936078.4577</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>92400985513.5217</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>94112481782.3699</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>96269106264.6511</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>99027351562.8589</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>101358250574.724</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>97281975327.6295</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>33254688392.1349</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>33803965620.9691</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>34560200350.4792</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>34940534397.1928</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>35410618444.7986</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>36447634006.3778</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>36163920153.2055</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>36478137797.8286</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>37023153586.8513</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>38065723252.6162</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>38656008037.4245</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>39422101863.7109</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>40211395303.3007</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>40470981408.468</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>39656294308.6401</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>13593006.8730362</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>13739222.1632323</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>14027669.99811</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>14345414.99821</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>14719774.99802</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>15048149.99801</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>15199154.99804</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>15568199.99803</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>15901974.99803</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>16165969.99803</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>16405414.99804</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>16676749.99804</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>17046849.99804</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>17485670.859599</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>16875446.8452208</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>12163122.9926407</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>12208770.2160367</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>12428724.99891</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>12680214.99891</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>13075604.99891</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>13480109.99891</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>13707879.99891</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>14047644.99891</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>14354944.99891</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>14633084.99891</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>14846974.99891</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>15135234.99891</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>15443969.99891</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>15744979.99891</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>15432784.99891</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>24163261022.4366</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>24606801459.0087</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>24972060998.11</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>25524080998.21</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>26167658998.02</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>26709974998.01</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>26868101998.04</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>27201948998.03</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>27611261998.03</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>28349859998.03</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>28533802998.04</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>28986531998.04</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>29625119998.04</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>30221823441.5849</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>28824294040.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>21474270065.9936</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>21728470234.0654</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>21998084998.91</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>22407135998.91</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>23096433998.91</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>23762494998.91</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>24065073998.91</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>24452872998.91</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>24822943998.91</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>25528032998.91</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>25761810998.91</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>26246007998.91</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>26776737998.91</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>27188562998.91</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>26224347998.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.165026836006221</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.174070473563283</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.18533569691959</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.191701460000232</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.19153353552202</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.196860559389073</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.205381127739414</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.208997566663107</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.211037923925837</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.216881218718759</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.222901783891316</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.233777121466238</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.240482936633715</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.235402302929652</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.248822892765799</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.777580178303824</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.773047863670747</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.764365399958455</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.76011374745345</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.765582903940644</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.763194950347046</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.756955280826279</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.753490805886111</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.753646248571463</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.749574489514505</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.745810508452688</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.735992500871819</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.732808213124645</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.738094910441187</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.725483562503862</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0573929821675975</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.0528816592979775</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.0502988998164565</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0481847893652541</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0428835575080581</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0399444874783705</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0376635887154743</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.0375116248191324</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0353158250441179</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0335442894785202</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.03128770542763</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0302303754872812</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0267088480864822</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0265027844380628</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0256935423471342</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.283887302200348</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.285670803300515</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.290353545121221</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.298563117887347</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.295937329398875</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.30465518606849</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.314558168088238</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.319333592254155</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.324247100564213</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.329304172845394</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.342471928600837</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.354529651891686</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.366693601378756</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.36334859640695</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.378855210793273</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.690684332302548</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.690398853786109</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.687386446496856</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.680037452762035</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.685018990794521</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.677638712463395</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.668973831811685</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.664060624245341</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.659763732827066</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.655572736587632</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.643562910100225</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.631862208699721</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.621306339865223</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.624793958567878</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.609462512069951</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0254283654971034</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.0239303429133753</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0222600083819227</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0213994293506188</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0190436798066037</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.017706101468115</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0164680001000778</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.016605783500504</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0159891666087209</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0151230905669744</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0139651612989379</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0136081394085931</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0120000587560204</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0118574450251713</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0116822771367762</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1026040.00237</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1080145.52527</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1130851.85394</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1099419.52822</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1188394.5984</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1332236.76032</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1314026.785</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1335753.48033</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1569015.20584</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1798475.86541</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2047279.31899</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2296688.91947</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2536378.0898</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2697549.842</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2392609.67465</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>547035.37625</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>569004.55983</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>590028.93518</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>571275.18468</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>612315.22592</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>673562.94928</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>666649.17545</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>681187.95021</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>808003.50894</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>924738.04722</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1057277.28328</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1191310.6512</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1322736.20347</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1406788.2493</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1247760.13746</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2478486.31468713</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2535886.67313897</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2611947.9277956</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2687320.32675744</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2769268.91957621</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2852903.90086274</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2935766.10277972</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>3017657.92971134</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>3109805.33179146</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>3216840.57326967</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>3342467.02234172</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>3482845.33662717</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>3624386.83491654</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3761457.24938902</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>3844141.95872883</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
